--- a/Result/profitability/9942.xlsx
+++ b/Result/profitability/9942.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9525</v>
+        <v>2.01375</v>
       </c>
       <c r="N2" t="n">
-        <v>38.42625</v>
+        <v>38.2925</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.11</v>
       </c>
       <c r="M3" t="n">
-        <v>1.835</v>
+        <v>1.85875</v>
       </c>
       <c r="N3" t="n">
-        <v>37.1175</v>
+        <v>37.16875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.9</v>
       </c>
       <c r="M4" t="n">
-        <v>1.65375</v>
+        <v>1.70125</v>
       </c>
       <c r="N4" t="n">
-        <v>35.91625</v>
+        <v>36.04375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.51</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4475</v>
+        <v>1.56125</v>
       </c>
       <c r="N5" t="n">
-        <v>34.6475</v>
+        <v>34.88125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.28625</v>
+        <v>1.32375</v>
       </c>
       <c r="N6" t="n">
-        <v>33.37375</v>
+        <v>33.385</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.66</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08875</v>
+        <v>1.14125</v>
       </c>
       <c r="N7" t="n">
-        <v>32.72875</v>
+        <v>32.84875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.59</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8975000000000001</v>
+        <v>0.9375</v>
       </c>
       <c r="N8" t="n">
-        <v>31.9</v>
+        <v>31.90875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9942</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1207</v>
+      </c>
+      <c r="D75" t="n">
+        <v>724</v>
+      </c>
+      <c r="E75" t="n">
+        <v>483</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>301</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>24.94%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>19</v>
+      </c>
+      <c r="J75" t="n">
+        <v>320</v>
+      </c>
+      <c r="K75" t="n">
+        <v>211</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.16375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.61125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3199999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.144144144144144</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.001751751751751796</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5582822085889572</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.870000000000005</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04900419287211744</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
